--- a/artfynd/A 66171-2021 artfynd.xlsx
+++ b/artfynd/A 66171-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66171-2021 artfynd.xlsx
+++ b/artfynd/A 66171-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97095145</v>
+        <v>105343465</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gideåberg, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579724.4839347757</v>
+        <v>579683</v>
       </c>
       <c r="R2" t="n">
-        <v>7017110.590887212</v>
+        <v>7017226</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97095148</v>
+        <v>105343470</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gideåberg, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579685.996330076</v>
+        <v>579660</v>
       </c>
       <c r="R3" t="n">
-        <v>7017226.265308863</v>
+        <v>7017170</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,34 +855,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97095132</v>
+        <v>105343478</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gideåberg, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579685.996330076</v>
+        <v>579577</v>
       </c>
       <c r="R4" t="n">
-        <v>7017226.265308863</v>
+        <v>7017345</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,62 +956,59 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97095122</v>
+        <v>97095145</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579548.2651212236</v>
+        <v>579724</v>
       </c>
       <c r="R5" t="n">
-        <v>7017307.51095837</v>
+        <v>7017111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,19 +1049,9 @@
           <t>2021-11-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,53 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97095139</v>
+        <v>105343466</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gideåberg, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579832.2034371081</v>
+        <v>579674</v>
       </c>
       <c r="R6" t="n">
-        <v>7017130.823614909</v>
+        <v>7017203</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,70 +1158,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104458873</v>
+        <v>105343476</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579780.8448125784</v>
+        <v>579578</v>
       </c>
       <c r="R7" t="n">
-        <v>7017238.071827815</v>
+        <v>7017310</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,22 +1270,21 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105343458</v>
+        <v>105343481</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579783.0421596091</v>
+        <v>579737</v>
       </c>
       <c r="R8" t="n">
-        <v>7017240.377768097</v>
+        <v>7017300</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,19 +1349,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105343459</v>
+        <v>105343477</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579772.722351916</v>
+        <v>579577</v>
       </c>
       <c r="R9" t="n">
-        <v>7017238.320730507</v>
+        <v>7017350</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,24 +1450,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst ett hundratal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105343456</v>
+        <v>105343469</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579804.8103872354</v>
+        <v>579660</v>
       </c>
       <c r="R10" t="n">
-        <v>7017253.525732107</v>
+        <v>7017172</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,19 +1551,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105343473</v>
+        <v>105343471</v>
       </c>
       <c r="B11" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1762,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579609.2000102183</v>
+        <v>579660</v>
       </c>
       <c r="R11" t="n">
-        <v>7017232.019263589</v>
+        <v>7017164</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1795,19 +1652,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105343483</v>
+        <v>97095132</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,34 +1696,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Gideåberg, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579783.1931797517</v>
+        <v>579686</v>
       </c>
       <c r="R12" t="n">
-        <v>7017307.02389033</v>
+        <v>7017226</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1908,22 +1753,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,37 +1767,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105343463</v>
+        <v>105343464</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579700.9005452361</v>
+        <v>579703</v>
       </c>
       <c r="R13" t="n">
-        <v>7017225.283579725</v>
+        <v>7017226</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2027,24 +1854,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105343452</v>
+        <v>105343468</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579816.6870382873</v>
+        <v>579675</v>
       </c>
       <c r="R14" t="n">
-        <v>7017265.527831624</v>
+        <v>7017185</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2148,19 +1955,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105343451</v>
+        <v>105343473</v>
       </c>
       <c r="B15" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2231,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579818.4895348814</v>
+        <v>579609</v>
       </c>
       <c r="R15" t="n">
-        <v>7017265.57254611</v>
+        <v>7017232</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2264,19 +2056,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,15 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105343480</v>
+        <v>105343482</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579711.1945722729</v>
+        <v>579766</v>
       </c>
       <c r="R16" t="n">
-        <v>7017301.186834521</v>
+        <v>7017303</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2380,19 +2157,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105343445</v>
+        <v>97095148</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,34 +2201,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Gideåberg, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579803.1208369432</v>
+        <v>579686</v>
       </c>
       <c r="R17" t="n">
-        <v>7017303.465553427</v>
+        <v>7017226</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2493,27 +2258,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett sjuttiotal</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,41 +2272,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105343707</v>
+        <v>105343461</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2584,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579687.9039745554</v>
+        <v>579708</v>
       </c>
       <c r="R18" t="n">
-        <v>7017240.271581493</v>
+        <v>7017233</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2614,22 +2356,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,37 +2397,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105343455</v>
+        <v>105343472</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2700,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579809.4993762716</v>
+        <v>579639</v>
       </c>
       <c r="R19" t="n">
-        <v>7017264.448961981</v>
+        <v>7017141</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2733,19 +2465,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,37 +2503,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105343454</v>
+        <v>105343480</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2816,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579810.4229496645</v>
+        <v>579711</v>
       </c>
       <c r="R20" t="n">
-        <v>7017263.571295053</v>
+        <v>7017301</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2849,19 +2571,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,37 +2604,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105343481</v>
+        <v>105343543</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2932,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579736.935617767</v>
+        <v>579619</v>
       </c>
       <c r="R21" t="n">
-        <v>7017299.573241754</v>
+        <v>7017127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2962,22 +2669,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,37 +2705,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105343468</v>
+        <v>105343707</v>
       </c>
       <c r="B22" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3048,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579674.3927387836</v>
+        <v>579688</v>
       </c>
       <c r="R22" t="n">
-        <v>7017185.001114439</v>
+        <v>7017240</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3078,22 +2770,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,15 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105343457</v>
+        <v>105343708</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579783.8764628416</v>
+        <v>579703</v>
       </c>
       <c r="R23" t="n">
-        <v>7017243.100200344</v>
+        <v>7017237</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3194,27 +2871,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 500 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3245,37 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105343469</v>
+        <v>105343458</v>
       </c>
       <c r="B24" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3285,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579659.8448691779</v>
+        <v>579783</v>
       </c>
       <c r="R24" t="n">
-        <v>7017171.582255266</v>
+        <v>7017240</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3318,19 +2980,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3361,37 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105343453</v>
+        <v>105343460</v>
       </c>
       <c r="B25" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3401,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579809.5217008232</v>
+        <v>579743</v>
       </c>
       <c r="R25" t="n">
-        <v>7017263.548939944</v>
+        <v>7017238</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3434,19 +3081,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,15 +3114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105343482</v>
+        <v>105343483</v>
       </c>
       <c r="B26" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,21 +3125,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3517,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579766.1589330904</v>
+        <v>579783</v>
       </c>
       <c r="R26" t="n">
-        <v>7017302.999287616</v>
+        <v>7017307</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3550,19 +3182,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,37 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105343449</v>
+        <v>105343710</v>
       </c>
       <c r="B27" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3633,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579835.3452696394</v>
+        <v>579787</v>
       </c>
       <c r="R27" t="n">
-        <v>7017276.797624341</v>
+        <v>7017243</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3663,22 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,15 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105343710</v>
+        <v>105343541</v>
       </c>
       <c r="B28" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3749,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579787.030853655</v>
+        <v>579651</v>
       </c>
       <c r="R28" t="n">
-        <v>7017243.178419056</v>
+        <v>7017278</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3779,22 +3381,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hona</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,15 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105343460</v>
+        <v>105343463</v>
       </c>
       <c r="B29" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3841,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3865,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579742.9809064743</v>
+        <v>579701</v>
       </c>
       <c r="R29" t="n">
-        <v>7017237.583495247</v>
+        <v>7017225</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3898,19 +3490,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3941,15 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105343464</v>
+        <v>110416012</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,37 +3539,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Djupdalsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579703.1313989196</v>
+        <v>579692</v>
       </c>
       <c r="R30" t="n">
-        <v>7017226.239424243</v>
+        <v>7017208</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4011,22 +3597,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Träd med ringhack av tretåig hackspett nersågat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4046,61 +3627,56 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105343466</v>
+        <v>97095122</v>
       </c>
       <c r="B31" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Gideåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579674.3976402115</v>
+        <v>579548</v>
       </c>
       <c r="R31" t="n">
-        <v>7017203.013099495</v>
+        <v>7017307</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4127,22 +3703,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4151,72 +3717,68 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105343461</v>
+        <v>97095124</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Gideåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579707.9211032181</v>
+        <v>579736</v>
       </c>
       <c r="R32" t="n">
-        <v>7017233.112451823</v>
+        <v>7017346</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4243,27 +3805,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4272,72 +3819,65 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105343476</v>
+        <v>104458873</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579577.972519167</v>
+        <v>579781</v>
       </c>
       <c r="R33" t="n">
-        <v>7017309.5964114</v>
+        <v>7017238</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4364,22 +3904,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4399,48 +3939,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105343450</v>
+        <v>105343457</v>
       </c>
       <c r="B34" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4450,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579838.5442931099</v>
+        <v>579784</v>
       </c>
       <c r="R34" t="n">
-        <v>7017275.07585623</v>
+        <v>7017243</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4483,19 +4014,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 500 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4526,37 +4052,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105343708</v>
+        <v>105343459</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4566,10 +4087,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579702.8638625352</v>
+        <v>579773</v>
       </c>
       <c r="R35" t="n">
-        <v>7017237.039794789</v>
+        <v>7017238</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4596,27 +4117,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Minst ett hundratal</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4647,37 +4158,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105343465</v>
+        <v>105343467</v>
       </c>
       <c r="B36" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4687,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>579682.8419233034</v>
+        <v>579668</v>
       </c>
       <c r="R36" t="n">
-        <v>7017226.187189312</v>
+        <v>7017192</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4720,19 +4226,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ett hundratal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4763,15 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105343467</v>
+        <v>105343475</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4803,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>579667.4549314573</v>
+        <v>579562</v>
       </c>
       <c r="R37" t="n">
-        <v>7017192.034087074</v>
+        <v>7017305</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4836,24 +4332,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ett hundratal</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,37 +4370,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105343711</v>
+        <v>105343709</v>
       </c>
       <c r="B38" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4405,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>579796.8442085281</v>
+        <v>579784</v>
       </c>
       <c r="R38" t="n">
-        <v>7017247.474391784</v>
+        <v>7017239</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4957,19 +4438,14 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5000,37 +4476,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105343475</v>
+        <v>105343448</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5040,10 +4511,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>579562.2899183927</v>
+        <v>579825</v>
       </c>
       <c r="R39" t="n">
-        <v>7017305.606333558</v>
+        <v>7017294</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5073,24 +4544,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5121,37 +4577,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105343446</v>
+        <v>105343450</v>
       </c>
       <c r="B40" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5161,10 +4612,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>579805.9250060807</v>
+        <v>579838</v>
       </c>
       <c r="R40" t="n">
-        <v>7017299.482562289</v>
+        <v>7017275</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5194,33 +4645,17 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Direkt på gräns till avverkningsanmälan där SCAs snitselband fladdrar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5243,15 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105343472</v>
+        <v>105343451</v>
       </c>
       <c r="B41" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5283,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>579638.9716862636</v>
+        <v>579818</v>
       </c>
       <c r="R41" t="n">
-        <v>7017140.445052639</v>
+        <v>7017266</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5316,24 +4746,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,37 +4779,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105343709</v>
+        <v>105343455</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5404,10 +4814,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>579783.9768909359</v>
+        <v>579810</v>
       </c>
       <c r="R42" t="n">
-        <v>7017239.0500726</v>
+        <v>7017265</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5434,27 +4844,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5485,37 +4880,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105343471</v>
+        <v>105343456</v>
       </c>
       <c r="B43" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5525,10 +4915,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>579660.0342707711</v>
+        <v>579805</v>
       </c>
       <c r="R43" t="n">
-        <v>7017163.931841948</v>
+        <v>7017253</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5558,19 +4948,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5601,15 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105343470</v>
+        <v>105343711</v>
       </c>
       <c r="B44" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5626,12 +5001,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5641,10 +5016,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>579659.8894342285</v>
+        <v>579797</v>
       </c>
       <c r="R44" t="n">
-        <v>7017169.782159647</v>
+        <v>7017247</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5671,22 +5046,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5717,15 +5082,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105343541</v>
+        <v>105343712</v>
       </c>
       <c r="B45" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5733,21 +5093,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100001</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5757,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>579650.4562294735</v>
+        <v>579911</v>
       </c>
       <c r="R45" t="n">
-        <v>7017277.618783335</v>
+        <v>7017269</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5787,27 +5147,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hona</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5838,15 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110416012</v>
+        <v>105343447</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5854,41 +5194,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>579692.311492136</v>
+        <v>579825</v>
       </c>
       <c r="R46" t="n">
-        <v>7017207.959680946</v>
+        <v>7017292</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5912,27 +5248,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Träd med ringhack av tretåig hackspett nersågat</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5952,10 +5273,944 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>105343454</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>579811</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7017264</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>97095139</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gideåberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>579832</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7017131</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-11-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-11-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>105343449</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>579835</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7017277</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>105343453</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>579810</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7017264</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>105343452</v>
+      </c>
+      <c r="B51" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>579816</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7017266</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105343446</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>579806</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7017299</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Direkt på gräns till avverkningsanmälan där SCAs snitselband fladdrar</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>105343443</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>579813</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7017345</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>105343444</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>579817</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7017348</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>105343445</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>579803</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7017304</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett sjuttiotal</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66171-2021 artfynd.xlsx
+++ b/artfynd/A 66171-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343456</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343465</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343470</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343478</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343711</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343712</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095145</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343447</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343454</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343466</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343476</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343481</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2387,6 +2472,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343477</t>
         </is>
       </c>
     </row>
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343449</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343453</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343469</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2892,6 +3002,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343471</t>
         </is>
       </c>
     </row>
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095132</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343452</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343464</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343468</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343473</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343482</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3605,6 +3750,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343446</t>
         </is>
       </c>
     </row>
@@ -3708,6 +3858,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095148</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3814,6 +3969,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343461</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3920,6 +4080,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343472</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4021,6 +4186,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343480</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4122,6 +4292,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343543</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4223,6 +4398,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343707</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4329,6 +4509,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343708</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4430,6 +4615,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343458</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4531,6 +4721,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343460</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4632,6 +4827,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343483</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4733,6 +4933,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343710</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343541</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4943,6 +5153,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343463</t>
         </is>
       </c>
     </row>
@@ -5051,6 +5266,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110416012</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5153,6 +5373,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095122</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5255,6 +5480,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97095124</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5363,6 +5593,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104458873</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5469,6 +5704,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343443</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5575,6 +5815,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343444</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5681,6 +5926,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343445</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5787,6 +6037,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343457</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5893,6 +6148,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343459</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5999,6 +6259,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343467</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6105,6 +6370,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343475</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6211,8 +6481,69 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>